--- a/Schedule2026-2.xlsx
+++ b/Schedule2026-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\KU2026Seminar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31863E49-DD17-4ECD-94F7-02C3F092335C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB11C5D6-064A-43EA-A54F-07019A646AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
   <si>
     <t>Chapter</t>
   </si>
@@ -207,6 +207,36 @@
   </si>
   <si>
     <t>Epi studies design (?)</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>4--5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>研究の準備 ?</t>
+  </si>
+  <si>
+    <t>論文発表 ?</t>
+  </si>
+  <si>
+    <t>1--3</t>
+  </si>
+  <si>
+    <t>11--12</t>
   </si>
 </sst>
 </file>
@@ -316,16 +346,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -408,15 +435,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -431,6 +449,35 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,22 +816,27 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="25" customWidth="1"/>
-    <col min="3" max="3" width="7.25" style="25" customWidth="1"/>
-    <col min="4" max="4" width="4.25" style="26" customWidth="1"/>
-    <col min="5" max="6" width="11.875" style="26" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="26" customWidth="1"/>
-    <col min="10" max="10" width="47.125" style="25" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="3.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="24" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="24" customWidth="1"/>
+    <col min="4" max="4" width="4.25" style="25" customWidth="1"/>
+    <col min="5" max="6" width="11.875" style="25" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="46" customWidth="1"/>
+    <col min="8" max="8" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="25" customWidth="1"/>
+    <col min="10" max="10" width="47.125" style="24" customWidth="1"/>
+    <col min="11" max="11" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" style="25" customWidth="1"/>
+    <col min="13" max="13" width="47.125" style="24" customWidth="1"/>
+    <col min="14" max="15" width="9" style="3"/>
+    <col min="16" max="16" width="9" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -792,959 +844,1325 @@
       <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="45" t="s">
         <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="L1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
         <v>2026</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>4</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="G2" s="42">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="27" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+      <c r="K2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="9">
+      <c r="E3" s="6"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="42">
+        <v>2</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="27" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+      <c r="K3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6">
         <v>3</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="E4" s="6"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="42">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="8">
         <v>5.4</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+      <c r="K4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="9">
+      <c r="E5" s="6"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="8">
         <v>5.6</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="M5" s="27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="9" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="M6" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6">
         <v>2</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="9" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="42">
+        <v>6</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="M7" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="9" t="s">
+      <c r="E8" s="6"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="42">
+        <v>7</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="27" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7">
+      <c r="K8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6">
         <v>4</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="9" t="s">
+      <c r="E9" s="6"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="42">
+        <v>8</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="25"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A10" s="11">
+      <c r="K9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="24"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11">
         <v>6</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>1</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="44" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42" t="s">
+      <c r="G10" s="42">
+        <v>9</v>
+      </c>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="25"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" s="11">
+      <c r="K10" s="36"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="24"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12">
         <v>2</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="42" t="s">
+      <c r="E11" s="12"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="42">
+        <v>10</v>
+      </c>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="11">
+      <c r="K11" s="36"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12">
         <v>3</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="42" t="s">
+      <c r="E12" s="12"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A13" s="11">
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12">
         <v>4</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="42" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="38" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" s="11">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
-        <v>7</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11">
+        <v>7</v>
+      </c>
+      <c r="D14" s="12">
         <v>1</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="11" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42">
+        <v>12</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="20">
+        <v>4</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="M14" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" s="11">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12">
         <v>2</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="11" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42">
+        <v>13</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="20">
+        <v>5</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="L15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="M15" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="11">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12">
         <v>3</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="11" t="s">
+      <c r="E16" s="12"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42">
+        <v>14</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="20">
+        <v>6</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="L16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="M16" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="11">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12">
         <v>4</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="11" t="s">
+      <c r="E17" s="12"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42">
+        <v>15</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="20">
+        <v>7</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="L17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="M17" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="11">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12">
-        <v>8</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11">
+        <v>8</v>
+      </c>
+      <c r="D18" s="12">
         <v>1</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="11" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42">
+        <v>16</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="20">
+        <v>8</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="L18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="M18" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16">
         <v>2</v>
       </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="17" t="s">
+      <c r="E19" s="16"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="20">
+        <v>10</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A20" s="14">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16">
+        <v>3</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A21" s="14">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16">
+        <v>4</v>
+      </c>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="47"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+    </row>
+    <row r="23" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="47"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A24" s="14">
+        <v>21</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15">
+        <v>10</v>
+      </c>
+      <c r="D24" s="16">
+        <v>1</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="42">
+        <v>1</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J24" s="15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="15">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17">
+      <c r="K24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25" s="14">
+        <v>22</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16">
+        <v>2</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="42">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A26" s="14">
+        <v>23</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16">
         <v>3</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="17" t="s">
+      <c r="E26" s="16"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="42">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="16">
+        <v>7</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A27" s="14">
+        <v>24</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16">
+        <v>4</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="42">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J27" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="15">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17">
+      <c r="K27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="16">
+        <v>7</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A28" s="14">
+        <v>25</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15">
+        <v>11</v>
+      </c>
+      <c r="D28" s="16">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="42">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="16">
+        <v>8</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="14">
+        <v>26</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16">
+        <v>2</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="42">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="16">
+        <v>8</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A30" s="14">
+        <v>27</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16">
+        <v>3</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="42">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="16">
+        <v>9</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A31" s="14">
+        <v>28</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16">
         <v>4</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-    </row>
-    <row r="23" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="15">
-        <v>21</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16">
+      <c r="E31" s="16"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="42">
+        <v>8</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I31" s="16">
+        <v>7</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" s="16">
+        <v>9</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A32" s="18">
+        <v>29</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19">
+        <v>12</v>
+      </c>
+      <c r="D32" s="20">
+        <v>1</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="42">
+        <v>9</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="16">
+        <v>7</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="20">
+        <v>3</v>
+      </c>
+      <c r="M32" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="17">
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A33" s="18">
+        <v>30</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20">
+        <v>2</v>
+      </c>
+      <c r="E33" s="20"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="42">
+        <v>10</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="16">
+        <v>8</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="20">
+        <v>4</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A34" s="18">
+        <v>31</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20">
+        <v>3</v>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="42">
+        <v>11</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I34" s="16">
+        <v>8</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L34" s="20">
+        <v>5</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A35" s="18">
+        <v>32</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20">
+        <v>4</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="42">
+        <v>12</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="16">
+        <v>9</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="20">
+        <v>6</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A36" s="18">
+        <v>33</v>
+      </c>
+      <c r="B36" s="19">
+        <v>2027</v>
+      </c>
+      <c r="C36" s="19">
         <v>1</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="15">
-        <v>22</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17">
+      <c r="D36" s="20">
+        <v>1</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="48">
+        <v>13</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" s="16">
+        <v>9</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="20">
+        <v>7</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A37" s="18">
+        <v>34</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20">
         <v>2</v>
       </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="15">
-        <v>23</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17">
+      <c r="E37" s="20"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="48">
+        <v>14</v>
+      </c>
+      <c r="H37" s="21"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="20">
+        <v>8</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A38" s="18">
+        <v>35</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="20">
         <v>3</v>
       </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="17">
-        <v>7</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" s="15">
-        <v>24</v>
-      </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17">
+      <c r="E38" s="20"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="48">
+        <v>15</v>
+      </c>
+      <c r="H38" s="21"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="20">
+        <v>10</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A39" s="21">
+        <v>36</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23">
         <v>4</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="17">
-        <v>7</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="15">
-        <v>25</v>
-      </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16">
-        <v>11</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="E39" s="23"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="49">
+        <v>16</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A40" s="21">
+        <v>37</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22">
+        <v>2</v>
+      </c>
+      <c r="D40" s="23">
         <v>1</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I28" s="17">
-        <v>8</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="15">
-        <v>26</v>
-      </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17">
+      <c r="E40" s="23"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="K40" s="21"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A41" s="21">
+        <v>38</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="23">
         <v>2</v>
       </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="17">
-        <v>8</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="15">
-        <v>27</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17">
+      <c r="E41" s="23"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="K41" s="21"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="22"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="21">
+        <v>39</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="23">
         <v>3</v>
       </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I30" s="17">
-        <v>9</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="15">
-        <v>28</v>
-      </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17">
+      <c r="E42" s="23"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="22"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="21">
+        <v>40</v>
+      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="23">
         <v>4</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I31" s="17">
-        <v>9</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="19">
-        <v>29</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20">
-        <v>12</v>
-      </c>
-      <c r="D32" s="21">
-        <v>1</v>
-      </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="21">
-        <v>3</v>
-      </c>
-      <c r="J32" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="19">
-        <v>30</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="21">
-        <v>2</v>
-      </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="21">
-        <v>4</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="19">
-        <v>31</v>
-      </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="21">
-        <v>3</v>
-      </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="21">
-        <v>5</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="19">
-        <v>32</v>
-      </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="21">
-        <v>4</v>
-      </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="21">
-        <v>6</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="19">
-        <v>33</v>
-      </c>
-      <c r="B36" s="20">
-        <v>2027</v>
-      </c>
-      <c r="C36" s="20">
-        <v>1</v>
-      </c>
-      <c r="D36" s="21">
-        <v>1</v>
-      </c>
-      <c r="E36" s="21"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="21">
-        <v>7</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A37" s="19">
-        <v>34</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="21">
-        <v>2</v>
-      </c>
-      <c r="E37" s="21"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="21">
-        <v>8</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A38" s="19">
-        <v>35</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="21">
-        <v>3</v>
-      </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="21">
-        <v>10</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A39" s="22">
-        <v>36</v>
-      </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="24">
-        <v>4</v>
-      </c>
-      <c r="E39" s="24"/>
-      <c r="F39" s="35"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A40" s="22">
-        <v>37</v>
-      </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23">
-        <v>2</v>
-      </c>
-      <c r="D40" s="24">
-        <v>1</v>
-      </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="35"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A41" s="22">
-        <v>38</v>
-      </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="24">
-        <v>2</v>
-      </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="35"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="23"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A42" s="22">
-        <v>39</v>
-      </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24">
-        <v>3</v>
-      </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="35"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="23"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A43" s="22">
-        <v>40</v>
-      </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="24">
-        <v>4</v>
-      </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="35"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="23"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A44" s="34"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="33"/>
-    </row>
-    <row r="45" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="I45" s="32"/>
-    </row>
-    <row r="46" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="10"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="J48" s="10"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="33"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="32"/>
+    </row>
+    <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="51"/>
+      <c r="I45" s="31"/>
+      <c r="L45" s="31"/>
+    </row>
+    <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="51"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="9"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="9"/>
+    </row>
+    <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="51"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="9"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="9"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J48" s="9"/>
+      <c r="M48" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="8">
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="F36:F39"/>
     <mergeCell ref="F2:F9"/>
-    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F13:F19"/>
+    <mergeCell ref="G5:G6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
